--- a/outputs/одна_установка_режим_параметрами_для_менеджера.xlsx
+++ b/outputs/одна_установка_режим_параметрами_для_менеджера.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Установить 1 раз" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Параметры режима" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Таймлайн (1 установка)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Время менеджера" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="11">
     <font>
       <name val="Calibri"/>
@@ -72,7 +75,7 @@
       <sz val="13"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -87,6 +90,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00375623"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6E0B4"/>
       </patternFill>
     </fill>
   </fills>
@@ -116,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -143,6 +151,19 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -930,4 +951,230 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>ВРЕМЯ МЕНЕДЖЕРА НА АВТОМАТИЗАЦИЮ — WB + OZON (2 магазина WB + 1 Ozon)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Часы в день. Этап 1-2 = контроль (подтверждения+отточка регламентов). Этап 3 = автономность (контроль по журналу).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Задача</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>WB (этап контроля)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Ozon (этап контроля)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Автономность (этап 3)</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Что делает менеджер</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Реклама</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C5" s="13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D5" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>подтверждать ставки/паузы, править регламент</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Цены</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C6" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D6" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>подтверждать изменения цен</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Остатки/поставки</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C7" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D7" s="13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>оформлять поставки (всегда вручную)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>SEO / кластеры</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C8" s="13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D8" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>проверять и публиковать карточки</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Вопросы/отзывы</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C9" s="13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D9" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>решения по сложным, спорам</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Проверка отчётов/журнала</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C10" s="13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D10" s="13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>смотреть метрики, ловить ошибки</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>ИТОГО часов/день</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C11" s="15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="D11" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="16" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Этап контроля (старт): WB 3.2 ч + Ozon 2.3 ч = 5.5 ч/день на всё. Это ~69% рабочего дня одного человека.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Этап автономности: всего 1.0 ч/день — остаётся только контроль по журналу и сложные случаи.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>Вывод: на старте (контроль) 1 менеджер занят ~на полдня по двум площадкам. После автономности — ~1 час/день, можно вести больше магазинов.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/outputs/одна_установка_режим_параметрами_для_менеджера.xlsx
+++ b/outputs/одна_установка_режим_параметрами_для_менеджера.xlsx
@@ -7,10 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Установить 1 раз" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Параметры режима" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Таймлайн (1 установка)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Время менеджера" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Сроки запуска" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Установить 1 раз" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Параметры режима" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Таймлайн (1 установка)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Время менеджера" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -74,6 +75,10 @@
       <color rgb="00375623"/>
       <sz val="13"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C55A11"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -124,7 +129,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -165,6 +170,16 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -530,6 +545,264 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>СРОКИ НАСТРОЙКИ: ПОДКЛЮЧИТЬ WB + OZON К СЕРВЕРУ И ЗАПУСТИТЬ ИИ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>До момента «ИИ начал работать» (собирает данные и предлагает действия). Рабочие дни.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Шаг</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Что делаем</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Время</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Кто</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Создать ключи: WB-токены (2 магазина), Ozon Client-Id+Api-Key, Claude API</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="inlineStr">
+        <is>
+          <t>0,5 дня</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>ты (в кабинетах)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Установить платформу на сервер (код, окружение, .env)</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="inlineStr">
+        <is>
+          <t>0,5 дня</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>я веду пошагово</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Подключить WB API + проверить (продажи, остатки, реклама)</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="inlineStr">
+        <is>
+          <t>1 день</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>я</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Подключить Ozon API + проверить (остатки, цены, аналитика)</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr">
+        <is>
+          <t>1 день</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>я</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Настроить задачи, ограничители, Telegram-алерты</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>0,5 дня</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>я</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Первый прогон сбора + проверка данных и расчётов</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="inlineStr">
+        <is>
+          <t>0,5 дня</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>я + ты проверяешь</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="inlineStr"/>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>ИТОГО до запуска ИИ (сбор + предложения)</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>~4 раб. дня</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>ДАЛЬШЕ (после запуска):</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="5" t="inlineStr"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Отточка регламентов под контролем менеджера</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>2-4 недели работы</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="5" t="inlineStr"/>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Перевод в авто по одной задаче (без переустановки)</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>+1 день на задачу</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="5" t="inlineStr"/>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Браузерный агент (клики в кабинете по регламенту) — ОТДЕЛЬНО</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>+3-5 дней</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>ИТОГ: через ~4 рабочих дня ИИ начнёт работать по WB и Ozon (сбор + предложения). Дальше — отточка и постепенный перевод в автомат.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -628,7 +901,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -787,7 +1060,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -953,7 +1226,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/outputs/одна_установка_режим_параметрами_для_менеджера.xlsx
+++ b/outputs/одна_установка_режим_параметрами_для_менеджера.xlsx
@@ -23,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -79,6 +79,11 @@
       <b val="1"/>
       <color rgb="00C55A11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00375623"/>
+      <sz val="12"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -129,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -180,6 +185,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -803,7 +814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -895,6 +906,93 @@
           <t>Нет. Раз на сервере — работает сам. Контроль на старте = подтверждения в Telegram, а не «смотреть в ПК».</t>
         </is>
       </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>ВРЕМЯ НАСТРОЙКИ (подключить WB+Ozon к серверу и запустить ИИ):</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>• Создать ключи (WB, Ozon, Claude API)</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>0,5 дня — твоя сторона</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="23" t="inlineStr">
+        <is>
+          <t>• Установка на сервер + .env</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>0,5 дня</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>• Подключить и проверить WB API</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>1 день</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="23" t="inlineStr">
+        <is>
+          <t>• Подключить и проверить Ozon API</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>1 день</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t>• Настройка задач, ограничителей, Telegram</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>0,5 дня</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="23" t="inlineStr">
+        <is>
+          <t>• Первый прогон сбора + проверка</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>0,5 дня</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="25" t="inlineStr">
+        <is>
+          <t>ИТОГО: ~4 рабочих дня до старта ИИ (сбор + предложения). Подробности — на вкладке «Сроки запуска».</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
